--- a/example data/group/Stats Multiple Comparison - Version 1.xlsx
+++ b/example data/group/Stats Multiple Comparison - Version 1.xlsx
@@ -464,7 +464,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -492,7 +492,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -520,7 +520,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -556,7 +556,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -584,7 +584,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -612,7 +612,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -648,7 +648,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -676,7 +676,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -704,7 +704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -740,7 +740,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -768,7 +768,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -796,7 +796,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -832,7 +832,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -860,7 +860,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -924,7 +924,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -952,7 +952,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -980,7 +980,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1016,7 +1016,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1044,7 +1044,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1072,7 +1072,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1108,7 +1108,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1136,7 +1136,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1164,7 +1164,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1200,7 +1200,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1228,7 +1228,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1256,7 +1256,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1292,7 +1292,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1320,7 +1320,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1348,7 +1348,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1384,7 +1384,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1412,7 +1412,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1440,7 +1440,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1476,7 +1476,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1504,7 +1504,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1532,7 +1532,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1568,7 +1568,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1596,7 +1596,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1624,7 +1624,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1660,7 +1660,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1688,7 +1688,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1716,7 +1716,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1752,7 +1752,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1780,7 +1780,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1808,7 +1808,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1844,7 +1844,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1872,7 +1872,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1900,7 +1900,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1936,7 +1936,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1964,7 +1964,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1992,7 +1992,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2028,7 +2028,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2056,7 +2056,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2084,7 +2084,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2120,7 +2120,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2148,7 +2148,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2176,7 +2176,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2212,7 +2212,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2240,7 +2240,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2268,7 +2268,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2304,7 +2304,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2332,7 +2332,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2360,7 +2360,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2396,7 +2396,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2424,7 +2424,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2452,7 +2452,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2488,7 +2488,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2516,7 +2516,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2544,7 +2544,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2580,7 +2580,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2608,7 +2608,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2636,7 +2636,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2672,7 +2672,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2700,7 +2700,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2728,7 +2728,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2812,7 +2812,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2840,7 +2840,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2868,7 +2868,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2906,7 +2906,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2934,7 +2934,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2962,7 +2962,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3000,7 +3000,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3028,7 +3028,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3056,7 +3056,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3094,7 +3094,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3122,7 +3122,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3150,7 +3150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3188,7 +3188,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3216,7 +3216,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3244,7 +3244,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3282,7 +3282,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3310,7 +3310,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3338,7 +3338,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3376,7 +3376,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -3404,7 +3404,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3432,7 +3432,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3470,7 +3470,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3498,7 +3498,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3526,7 +3526,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3564,7 +3564,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3592,7 +3592,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3620,7 +3620,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3658,7 +3658,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3686,7 +3686,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3714,7 +3714,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3752,7 +3752,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3780,7 +3780,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3808,7 +3808,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3846,7 +3846,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3874,7 +3874,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3902,7 +3902,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3940,7 +3940,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3968,7 +3968,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3996,7 +3996,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4034,7 +4034,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4062,7 +4062,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4090,7 +4090,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4128,7 +4128,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4156,7 +4156,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4184,7 +4184,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4222,7 +4222,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4250,7 +4250,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4278,7 +4278,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4316,7 +4316,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4344,7 +4344,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4372,7 +4372,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4410,7 +4410,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4438,7 +4438,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4466,7 +4466,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4504,7 +4504,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -4532,7 +4532,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4560,7 +4560,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4598,7 +4598,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4626,7 +4626,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4654,7 +4654,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4692,7 +4692,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4720,7 +4720,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4748,7 +4748,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4786,7 +4786,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4814,7 +4814,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4842,7 +4842,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4880,7 +4880,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4908,7 +4908,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4936,7 +4936,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4974,7 +4974,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5002,7 +5002,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -5030,7 +5030,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -5068,7 +5068,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5mm &amp; 12mm</t>
+          <t>5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -5096,7 +5096,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5mm &amp; 25mm</t>
+          <t>5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5124,7 +5124,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>12mm &amp; 25mm</t>
+          <t>12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="B126" t="n">
